--- a/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCEBB63-9BFA-4AB6-A5EF-9430773792C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921150A3-01E1-4CF0-B193-EADDA616C94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="193">
   <si>
     <t>_FoodName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1029,10 +1029,6 @@
     <t>Assets/05.Animations/EffectAnimation/LaserEffect.prefab</t>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_m.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_f.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1041,7 +1037,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_s.prefab</t>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_sr.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_st.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1700,7 +1704,7 @@
         <v>139</v>
       </c>
       <c r="N5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>32</v>
@@ -1877,7 +1881,7 @@
         <v>139</v>
       </c>
       <c r="N8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>40</v>
@@ -2290,7 +2294,7 @@
         <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>51</v>
@@ -2585,7 +2589,7 @@
         <v>139</v>
       </c>
       <c r="N20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>61</v>
@@ -2998,7 +3002,7 @@
         <v>139</v>
       </c>
       <c r="N27" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>70</v>
@@ -3352,7 +3356,7 @@
         <v>139</v>
       </c>
       <c r="N33" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>81</v>
@@ -4060,7 +4064,7 @@
         <v>139</v>
       </c>
       <c r="N45" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>160</v>
@@ -4119,7 +4123,7 @@
         <v>139</v>
       </c>
       <c r="N46" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>133</v>
@@ -4473,7 +4477,7 @@
         <v>139</v>
       </c>
       <c r="N52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>113</v>
@@ -4827,7 +4831,7 @@
         <v>139</v>
       </c>
       <c r="N58" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>119</v>
@@ -4945,7 +4949,7 @@
         <v>139</v>
       </c>
       <c r="N60" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>127</v>

--- a/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921150A3-01E1-4CF0-B193-EADDA616C94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C26B6-457B-444F-80D4-8CDCA3B2AA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
@@ -1026,9 +1026,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/05.Animations/EffectAnimation/LaserEffect.prefab</t>
-  </si>
-  <si>
     <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_f.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1046,6 +1043,10 @@
   </si>
   <si>
     <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_st.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1592,7 +1593,7 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q3">
         <v>187</v>
@@ -1704,7 +1705,7 @@
         <v>139</v>
       </c>
       <c r="N5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>32</v>
@@ -1828,7 +1829,7 @@
         <v>142</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q7">
         <v>217</v>
@@ -1881,7 +1882,7 @@
         <v>139</v>
       </c>
       <c r="N8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>40</v>
@@ -2123,7 +2124,7 @@
         <v>43</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q12">
         <v>219</v>
@@ -2241,7 +2242,7 @@
         <v>167</v>
       </c>
       <c r="P14" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q14">
         <v>252</v>
@@ -2294,7 +2295,7 @@
         <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>51</v>
@@ -2477,7 +2478,7 @@
         <v>54</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>171</v>
@@ -2589,7 +2590,7 @@
         <v>139</v>
       </c>
       <c r="N20" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>61</v>
@@ -3002,7 +3003,7 @@
         <v>139</v>
       </c>
       <c r="N27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>70</v>
@@ -3185,7 +3186,7 @@
         <v>73</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q30">
         <v>241</v>
@@ -3356,7 +3357,7 @@
         <v>139</v>
       </c>
       <c r="N33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>81</v>
@@ -3539,7 +3540,7 @@
         <v>84</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>227</v>
@@ -3769,7 +3770,7 @@
         <v>139</v>
       </c>
       <c r="N40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>92</v>
@@ -3952,7 +3953,7 @@
         <v>95</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q43">
         <v>172</v>
@@ -4064,7 +4065,7 @@
         <v>139</v>
       </c>
       <c r="N45" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>160</v>
@@ -4123,7 +4124,7 @@
         <v>139</v>
       </c>
       <c r="N46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>133</v>
@@ -4306,7 +4307,7 @@
         <v>104</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q49">
         <v>185</v>
@@ -4477,7 +4478,7 @@
         <v>139</v>
       </c>
       <c r="N52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>113</v>
@@ -4660,7 +4661,7 @@
         <v>116</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>233</v>
@@ -4831,7 +4832,7 @@
         <v>139</v>
       </c>
       <c r="N58" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>119</v>
@@ -4949,7 +4950,7 @@
         <v>139</v>
       </c>
       <c r="N60" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>127</v>
@@ -5132,7 +5133,7 @@
         <v>130</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q63">
         <v>182</v>
@@ -5244,7 +5245,7 @@
         <v>139</v>
       </c>
       <c r="N65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>132</v>

--- a/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415C26B6-457B-444F-80D4-8CDCA3B2AA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751EB1AA-43FC-4F12-AE1E-B9250DBC9A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="12390" yWindow="600" windowWidth="13860" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodDatas" sheetId="1" r:id="rId1"/>
@@ -990,63 +990,68 @@
 7</t>
   </si>
   <si>
+    <t>15
+7</t>
+  </si>
+  <si>
+    <t>6
+4</t>
+  </si>
+  <si>
+    <t>4
+4</t>
+  </si>
+  <si>
+    <t>Assets/05.Animations/EffectAnimation/FireEffect.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_f.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_c.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_sr.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_st.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>5
 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7
+6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>9
 6</t>
-  </si>
-  <si>
-    <t>15
-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6
+6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>8
 6</t>
-  </si>
-  <si>
-    <t>6
-4</t>
-  </si>
-  <si>
-    <t>4
-4</t>
-  </si>
-  <si>
-    <t>7
-6</t>
-  </si>
-  <si>
-    <t>6
-6</t>
-  </si>
-  <si>
-    <t>Assets/05.Animations/EffectAnimation/FireEffect.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_f.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_c.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_sr.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_st.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1504,22 +1509,22 @@
         <v>21</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H2">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I2">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="J2">
         <v>0.5</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>173</v>
@@ -1534,7 +1539,7 @@
         <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>211</v>
@@ -1563,22 +1568,22 @@
         <v>21</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="I3">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J3">
         <v>0.5</v>
       </c>
       <c r="K3">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
@@ -1593,7 +1598,7 @@
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q3">
         <v>187</v>
@@ -1622,16 +1627,16 @@
         <v>21</v>
       </c>
       <c r="F4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G4">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
+        <v>0.83</v>
+      </c>
+      <c r="I4">
         <v>0.8</v>
-      </c>
-      <c r="I4">
-        <v>0.7</v>
       </c>
       <c r="J4">
         <v>0.5</v>
@@ -1652,7 +1657,7 @@
         <v>30</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q4">
         <v>255</v>
@@ -1705,13 +1710,13 @@
         <v>139</v>
       </c>
       <c r="N5" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q5">
         <v>166</v>
@@ -1740,16 +1745,16 @@
         <v>21</v>
       </c>
       <c r="F6">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="I6">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J6">
         <v>0.5</v>
@@ -1770,7 +1775,7 @@
         <v>33</v>
       </c>
       <c r="P6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>199</v>
@@ -1829,7 +1834,7 @@
         <v>142</v>
       </c>
       <c r="P7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q7">
         <v>217</v>
@@ -1858,22 +1863,22 @@
         <v>39</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="H8">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J8">
         <v>0.5</v>
       </c>
       <c r="K8">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -1882,13 +1887,13 @@
         <v>139</v>
       </c>
       <c r="N8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>40</v>
       </c>
       <c r="P8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q8">
         <v>254</v>
@@ -1917,16 +1922,16 @@
         <v>39</v>
       </c>
       <c r="F9">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H9">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="I9">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J9">
         <v>0.5</v>
@@ -1947,7 +1952,7 @@
         <v>41</v>
       </c>
       <c r="P9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q9">
         <v>219</v>
@@ -1979,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>0.85</v>
@@ -2006,7 +2011,7 @@
         <v>42</v>
       </c>
       <c r="P10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q10">
         <v>255</v>
@@ -2035,16 +2040,16 @@
         <v>39</v>
       </c>
       <c r="F11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H11">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="I11">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J11">
         <v>0.5</v>
@@ -2065,7 +2070,7 @@
         <v>144</v>
       </c>
       <c r="P11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>255</v>
@@ -2094,22 +2099,22 @@
         <v>39</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I12">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J12">
         <v>0.5</v>
       </c>
       <c r="K12">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2124,7 +2129,7 @@
         <v>43</v>
       </c>
       <c r="P12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q12">
         <v>219</v>
@@ -2153,25 +2158,25 @@
         <v>39</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="G13">
-        <v>6</v>
+        <v>5.15</v>
       </c>
       <c r="H13">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="I13">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="J13">
         <v>0.5</v>
       </c>
       <c r="K13">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="M13" t="s">
         <v>139</v>
@@ -2183,7 +2188,7 @@
         <v>44</v>
       </c>
       <c r="P13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q13">
         <v>128</v>
@@ -2212,16 +2217,16 @@
         <v>39</v>
       </c>
       <c r="F14">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I14">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J14">
         <v>0.5</v>
@@ -2242,7 +2247,7 @@
         <v>167</v>
       </c>
       <c r="P14" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q14">
         <v>252</v>
@@ -2274,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15">
         <v>0.5</v>
@@ -2295,13 +2300,13 @@
         <v>139</v>
       </c>
       <c r="N15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>51</v>
       </c>
       <c r="P15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q15">
         <v>135</v>
@@ -2333,7 +2338,7 @@
         <v>3.3</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16">
         <v>0.25</v>
@@ -2360,7 +2365,7 @@
         <v>52</v>
       </c>
       <c r="P16" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q16">
         <v>242</v>
@@ -2389,22 +2394,22 @@
         <v>45</v>
       </c>
       <c r="F17">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="G17">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="H17">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="I17">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J17">
         <v>0.5</v>
       </c>
       <c r="K17">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>175</v>
@@ -2419,7 +2424,7 @@
         <v>53</v>
       </c>
       <c r="P17" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q17">
         <v>160</v>
@@ -2448,22 +2453,22 @@
         <v>45</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="I18">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="J18">
         <v>0.5</v>
       </c>
       <c r="K18">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L18" s="1">
         <v>0</v>
@@ -2478,7 +2483,7 @@
         <v>54</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q18">
         <v>171</v>
@@ -2507,25 +2512,25 @@
         <v>45</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I19">
-        <v>1.1000000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="J19">
         <v>0.5</v>
       </c>
       <c r="K19">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M19" t="s">
         <v>139</v>
@@ -2537,7 +2542,7 @@
         <v>55</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>255</v>
@@ -2566,22 +2571,22 @@
         <v>60</v>
       </c>
       <c r="F20">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H20">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="I20">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>0.5</v>
       </c>
       <c r="K20">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -2590,13 +2595,13 @@
         <v>139</v>
       </c>
       <c r="N20" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>61</v>
       </c>
       <c r="P20" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>192</v>
@@ -2625,16 +2630,16 @@
         <v>60</v>
       </c>
       <c r="F21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G21">
-        <v>6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H21">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="I21">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="J21">
         <v>0.5</v>
@@ -2655,7 +2660,7 @@
         <v>62</v>
       </c>
       <c r="P21" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>229</v>
@@ -2684,22 +2689,22 @@
         <v>60</v>
       </c>
       <c r="F22">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="H22">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="I22">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22">
         <v>0.5</v>
       </c>
       <c r="K22">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>176</v>
@@ -2714,7 +2719,7 @@
         <v>63</v>
       </c>
       <c r="P22" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q22">
         <v>159</v>
@@ -2743,25 +2748,25 @@
         <v>60</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H23">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I23">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J23">
         <v>0.5</v>
       </c>
       <c r="K23">
-        <v>0.05</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="L23">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M23" t="s">
         <v>139</v>
@@ -2773,7 +2778,7 @@
         <v>147</v>
       </c>
       <c r="P23" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>255</v>
@@ -2802,25 +2807,25 @@
         <v>60</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I24">
+        <v>1.2</v>
+      </c>
+      <c r="J24">
+        <v>0.5</v>
+      </c>
+      <c r="K24">
+        <v>0.13</v>
+      </c>
+      <c r="L24">
         <v>1.1000000000000001</v>
-      </c>
-      <c r="J24">
-        <v>0.5</v>
-      </c>
-      <c r="K24">
-        <v>0.1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
       </c>
       <c r="M24" t="s">
         <v>139</v>
@@ -2832,7 +2837,7 @@
         <v>134</v>
       </c>
       <c r="P24" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q24">
         <v>255</v>
@@ -2861,16 +2866,16 @@
         <v>60</v>
       </c>
       <c r="F25">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H25">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="I25">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25">
         <v>0.5</v>
@@ -2879,7 +2884,7 @@
         <v>0.02</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M25" t="s">
         <v>139</v>
@@ -2891,7 +2896,7 @@
         <v>149</v>
       </c>
       <c r="P25" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q25">
         <v>255</v>
@@ -2923,7 +2928,7 @@
         <v>3</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -2950,7 +2955,7 @@
         <v>151</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q26">
         <v>255</v>
@@ -2979,16 +2984,16 @@
         <v>69</v>
       </c>
       <c r="F27">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H27">
-        <v>0.5</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="I27">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J27">
         <v>0.5</v>
@@ -3003,13 +3008,13 @@
         <v>139</v>
       </c>
       <c r="N27" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>70</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q27">
         <v>216</v>
@@ -3038,16 +3043,16 @@
         <v>69</v>
       </c>
       <c r="F28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G28">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H28">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="I28">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J28">
         <v>0.5</v>
@@ -3068,7 +3073,7 @@
         <v>71</v>
       </c>
       <c r="P28" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q28">
         <v>226</v>
@@ -3097,22 +3102,22 @@
         <v>69</v>
       </c>
       <c r="F29">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="H29">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="I29">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J29">
         <v>0.5</v>
       </c>
       <c r="K29">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L29" s="1" t="s">
         <v>177</v>
@@ -3127,7 +3132,7 @@
         <v>72</v>
       </c>
       <c r="P29" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q29">
         <v>111</v>
@@ -3159,7 +3164,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H30">
         <v>0.17</v>
@@ -3186,7 +3191,7 @@
         <v>73</v>
       </c>
       <c r="P30" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q30">
         <v>241</v>
@@ -3215,25 +3220,25 @@
         <v>69</v>
       </c>
       <c r="F31">
-        <v>7.6</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G31">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="H31">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I31">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0.5</v>
       </c>
       <c r="K31">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="s">
         <v>139</v>
@@ -3245,7 +3250,7 @@
         <v>74</v>
       </c>
       <c r="P31" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q31">
         <v>255</v>
@@ -3277,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>0.9</v>
@@ -3292,7 +3297,7 @@
         <v>0.1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s">
         <v>139</v>
@@ -3304,7 +3309,7 @@
         <v>153</v>
       </c>
       <c r="P32" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q32">
         <v>249</v>
@@ -3333,16 +3338,16 @@
         <v>80</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="H33">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="I33">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J33">
         <v>0.5</v>
@@ -3357,13 +3362,13 @@
         <v>139</v>
       </c>
       <c r="N33" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>81</v>
       </c>
       <c r="P33" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q33">
         <v>107</v>
@@ -3392,16 +3397,16 @@
         <v>80</v>
       </c>
       <c r="F34">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H34">
+        <v>0.26</v>
+      </c>
+      <c r="I34">
         <v>0.25</v>
-      </c>
-      <c r="I34">
-        <v>0.2</v>
       </c>
       <c r="J34">
         <v>0.5</v>
@@ -3422,7 +3427,7 @@
         <v>82</v>
       </c>
       <c r="P34" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q34">
         <v>199</v>
@@ -3451,16 +3456,16 @@
         <v>80</v>
       </c>
       <c r="F35">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="H35">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="I35">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J35">
         <v>0.5</v>
@@ -3469,7 +3474,7 @@
         <v>0.03</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="M35" t="s">
         <v>139</v>
@@ -3481,7 +3486,7 @@
         <v>83</v>
       </c>
       <c r="P35" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q35">
         <v>250</v>
@@ -3540,7 +3545,7 @@
         <v>84</v>
       </c>
       <c r="P36" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q36">
         <v>227</v>
@@ -3569,25 +3574,25 @@
         <v>80</v>
       </c>
       <c r="F37">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="G37">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H37">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="I37">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J37">
         <v>0.5</v>
       </c>
       <c r="K37">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L37">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="M37" t="s">
         <v>139</v>
@@ -3599,7 +3604,7 @@
         <v>85</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q37">
         <v>255</v>
@@ -3628,25 +3633,25 @@
         <v>80</v>
       </c>
       <c r="F38">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G38">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H38">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="I38">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J38">
         <v>0.5</v>
       </c>
       <c r="K38">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="s">
         <v>139</v>
@@ -3658,7 +3663,7 @@
         <v>156</v>
       </c>
       <c r="P38" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q38">
         <v>255</v>
@@ -3705,7 +3710,7 @@
         <v>0.05</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M39" t="s">
         <v>139</v>
@@ -3717,7 +3722,7 @@
         <v>158</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q39">
         <v>243</v>
@@ -3746,16 +3751,16 @@
         <v>157</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="G40">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="H40">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="I40">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J40">
         <v>0.5</v>
@@ -3770,13 +3775,13 @@
         <v>139</v>
       </c>
       <c r="N40" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>92</v>
       </c>
       <c r="P40" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q40">
         <v>254</v>
@@ -3835,7 +3840,7 @@
         <v>93</v>
       </c>
       <c r="P41" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q41">
         <v>226</v>
@@ -3864,25 +3869,25 @@
         <v>91</v>
       </c>
       <c r="F42">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="G42">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="H42">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="I42">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J42">
         <v>0.5</v>
       </c>
       <c r="K42">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="M42" t="s">
         <v>139</v>
@@ -3894,7 +3899,7 @@
         <v>94</v>
       </c>
       <c r="P42" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q42">
         <v>228</v>
@@ -3923,16 +3928,16 @@
         <v>91</v>
       </c>
       <c r="F43">
-        <v>2.2999999999999998</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="G43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H43">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="I43">
-        <v>0.5</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J43">
         <v>0.5</v>
@@ -3953,7 +3958,7 @@
         <v>95</v>
       </c>
       <c r="P43" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q43">
         <v>172</v>
@@ -3982,16 +3987,16 @@
         <v>91</v>
       </c>
       <c r="F44">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H44">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="I44">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J44">
         <v>0.5</v>
@@ -4012,7 +4017,7 @@
         <v>96</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q44">
         <v>255</v>
@@ -4041,22 +4046,22 @@
         <v>101</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>2.95</v>
       </c>
       <c r="H45">
         <v>0.6</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J45">
         <v>0.5</v>
       </c>
       <c r="K45">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -4065,13 +4070,13 @@
         <v>139</v>
       </c>
       <c r="N45" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>160</v>
       </c>
       <c r="P45" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q45">
         <v>173</v>
@@ -4124,13 +4129,13 @@
         <v>139</v>
       </c>
       <c r="N46" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>133</v>
       </c>
       <c r="P46" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q46">
         <v>59</v>
@@ -4159,22 +4164,22 @@
         <v>101</v>
       </c>
       <c r="F47">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="G47">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H47">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="I47">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="J47">
         <v>0.5</v>
       </c>
       <c r="K47">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -4189,7 +4194,7 @@
         <v>102</v>
       </c>
       <c r="P47" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q47">
         <v>230</v>
@@ -4218,25 +4223,25 @@
         <v>101</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="I48">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J48">
         <v>0.5</v>
       </c>
       <c r="K48">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M48" t="s">
         <v>139</v>
@@ -4248,7 +4253,7 @@
         <v>103</v>
       </c>
       <c r="P48" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q48">
         <v>111</v>
@@ -4280,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H49">
         <v>0.2</v>
@@ -4307,7 +4312,7 @@
         <v>104</v>
       </c>
       <c r="P49" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q49">
         <v>185</v>
@@ -4366,7 +4371,7 @@
         <v>163</v>
       </c>
       <c r="P50" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q50">
         <v>255</v>
@@ -4398,7 +4403,7 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -4413,7 +4418,7 @@
         <v>0.1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M51" t="s">
         <v>139</v>
@@ -4425,7 +4430,7 @@
         <v>164</v>
       </c>
       <c r="P51" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q51">
         <v>218</v>
@@ -4454,16 +4459,16 @@
         <v>112</v>
       </c>
       <c r="F52">
-        <v>7</v>
+        <v>7.15</v>
       </c>
       <c r="G52">
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="J52">
         <v>0.5</v>
@@ -4478,13 +4483,13 @@
         <v>139</v>
       </c>
       <c r="N52" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>113</v>
       </c>
       <c r="P52" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q52">
         <v>145</v>
@@ -4543,7 +4548,7 @@
         <v>114</v>
       </c>
       <c r="P53" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>233</v>
@@ -4572,16 +4577,16 @@
         <v>112</v>
       </c>
       <c r="F54">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G54">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H54">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="I54">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J54">
         <v>0.5</v>
@@ -4590,7 +4595,7 @@
         <v>0.03</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M54" t="s">
         <v>139</v>
@@ -4602,7 +4607,7 @@
         <v>115</v>
       </c>
       <c r="P54" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>210</v>
@@ -4631,16 +4636,16 @@
         <v>112</v>
       </c>
       <c r="F55">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G55">
         <v>7</v>
       </c>
       <c r="H55">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="I55">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J55">
         <v>0.5</v>
@@ -4661,7 +4666,7 @@
         <v>116</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q55">
         <v>233</v>
@@ -4690,22 +4695,22 @@
         <v>112</v>
       </c>
       <c r="F56">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="G56">
         <v>9</v>
       </c>
       <c r="H56">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="I56">
-        <v>0.7</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J56">
         <v>0.5</v>
       </c>
       <c r="K56">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L56">
         <v>2.5</v>
@@ -4720,7 +4725,7 @@
         <v>117</v>
       </c>
       <c r="P56" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q56">
         <v>255</v>
@@ -4749,25 +4754,25 @@
         <v>112</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="G57">
-        <v>6</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H57">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="I57">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57">
         <v>0.5</v>
       </c>
       <c r="K57">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L57">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M57" t="s">
         <v>139</v>
@@ -4779,7 +4784,7 @@
         <v>118</v>
       </c>
       <c r="P57" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>255</v>
@@ -4808,22 +4813,22 @@
         <v>112</v>
       </c>
       <c r="F58">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="H58">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="J58">
         <v>0.5</v>
       </c>
       <c r="K58">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -4832,13 +4837,13 @@
         <v>139</v>
       </c>
       <c r="N58" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>119</v>
       </c>
       <c r="P58" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>173</v>
@@ -4867,22 +4872,22 @@
         <v>126</v>
       </c>
       <c r="F59">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="G59">
         <v>9</v>
       </c>
       <c r="H59">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="I59">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J59">
         <v>0.5</v>
       </c>
       <c r="K59">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L59">
         <v>2.5</v>
@@ -4897,7 +4902,7 @@
         <v>166</v>
       </c>
       <c r="P59" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q59">
         <v>255</v>
@@ -4929,7 +4934,7 @@
         <v>4</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H60">
         <v>0.6</v>
@@ -4950,13 +4955,13 @@
         <v>139</v>
       </c>
       <c r="N60" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>239</v>
@@ -4988,7 +4993,7 @@
         <v>2</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H61">
         <v>0.3</v>
@@ -5015,7 +5020,7 @@
         <v>128</v>
       </c>
       <c r="P61" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q61">
         <v>209</v>
@@ -5062,7 +5067,7 @@
         <v>0.03</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M62" t="s">
         <v>139</v>
@@ -5074,7 +5079,7 @@
         <v>129</v>
       </c>
       <c r="P62" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>239</v>
@@ -5103,16 +5108,16 @@
         <v>126</v>
       </c>
       <c r="F63">
-        <v>2.2999999999999998</v>
+        <v>2.15</v>
       </c>
       <c r="G63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H63">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="I63">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="J63">
         <v>0.5</v>
@@ -5133,7 +5138,7 @@
         <v>130</v>
       </c>
       <c r="P63" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="Q63">
         <v>182</v>
@@ -5162,25 +5167,25 @@
         <v>126</v>
       </c>
       <c r="F64">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H64">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="I64">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J64">
         <v>0.5</v>
       </c>
       <c r="K64">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L64">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M64" t="s">
         <v>139</v>
@@ -5192,7 +5197,7 @@
         <v>131</v>
       </c>
       <c r="P64" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q64">
         <v>255</v>
@@ -5221,22 +5226,22 @@
         <v>126</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="H65">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J65">
         <v>0.5</v>
       </c>
       <c r="K65">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5245,13 +5250,13 @@
         <v>139</v>
       </c>
       <c r="N65" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>132</v>
       </c>
       <c r="P65" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>237</v>

--- a/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{751EB1AA-43FC-4F12-AE1E-B9250DBC9A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5155F6B8-EC26-495E-9DE7-7C0333884EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12390" yWindow="600" windowWidth="13860" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodDatas" sheetId="1" r:id="rId1"/>
@@ -1512,7 +1512,7 @@
         <v>4.1500000000000004</v>
       </c>
       <c r="G2">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H2">
         <v>0.95</v>
@@ -1571,7 +1571,7 @@
         <v>0.9</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>0.16</v>
@@ -1630,7 +1630,7 @@
         <v>7.8</v>
       </c>
       <c r="G4">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="H4">
         <v>0.83</v>
@@ -1689,7 +1689,7 @@
         <v>8.6</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>0.45</v>
@@ -1748,7 +1748,7 @@
         <v>3.5</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H6">
         <v>0.27</v>
@@ -1807,7 +1807,7 @@
         <v>2.9</v>
       </c>
       <c r="G7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7">
         <v>0.15</v>
@@ -1866,7 +1866,7 @@
         <v>3.6</v>
       </c>
       <c r="G8">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="H8">
         <v>0.5</v>
@@ -1925,7 +1925,7 @@
         <v>3.1</v>
       </c>
       <c r="G9">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="H9">
         <v>0.23</v>
@@ -1984,7 +1984,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>0.85</v>
@@ -2043,7 +2043,7 @@
         <v>7.4</v>
       </c>
       <c r="G11">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="H11">
         <v>0.77</v>
@@ -2102,7 +2102,7 @@
         <v>0.8</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>0.15</v>
@@ -2161,7 +2161,7 @@
         <v>3.85</v>
       </c>
       <c r="G13">
-        <v>5.15</v>
+        <v>6.15</v>
       </c>
       <c r="H13">
         <v>0.85</v>
@@ -2220,7 +2220,7 @@
         <v>3</v>
       </c>
       <c r="G14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14">
         <v>0.16</v>
@@ -2279,7 +2279,7 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>0.5</v>
@@ -2338,7 +2338,7 @@
         <v>3.3</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>0.25</v>
@@ -2397,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -2456,7 +2456,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18">
         <v>0.22</v>
@@ -2515,7 +2515,7 @@
         <v>2.8</v>
       </c>
       <c r="G19">
-        <v>3.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H19">
         <v>0.9</v>
@@ -2574,7 +2574,7 @@
         <v>6.7</v>
       </c>
       <c r="G20">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="H20">
         <v>0.47</v>
@@ -2633,7 +2633,7 @@
         <v>3.2</v>
       </c>
       <c r="G21">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="H21">
         <v>0.24</v>
@@ -2692,7 +2692,7 @@
         <v>6.7</v>
       </c>
       <c r="G22">
-        <v>9.1999999999999993</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="H22">
         <v>0.87</v>
@@ -2751,7 +2751,7 @@
         <v>5.6</v>
       </c>
       <c r="G23">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H23">
         <v>0.8</v>
@@ -2810,7 +2810,7 @@
         <v>3.2</v>
       </c>
       <c r="G24">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="H24">
         <v>1.1000000000000001</v>
@@ -2869,7 +2869,7 @@
         <v>7.2</v>
       </c>
       <c r="G25">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H25">
         <v>0.74</v>
@@ -2928,7 +2928,7 @@
         <v>3</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -2987,7 +2987,7 @@
         <v>6.85</v>
       </c>
       <c r="G27">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="H27">
         <v>0.48499999999999999</v>
@@ -3046,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="G28">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="H28">
         <v>0.21</v>
@@ -3105,7 +3105,7 @@
         <v>6.2</v>
       </c>
       <c r="G29">
-        <v>8.8000000000000007</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="H29">
         <v>0.73</v>
@@ -3164,7 +3164,7 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H30">
         <v>0.17</v>
@@ -3223,7 +3223,7 @@
         <v>8.1999999999999993</v>
       </c>
       <c r="G31">
-        <v>7.3</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="H31">
         <v>0.9</v>
@@ -3282,7 +3282,7 @@
         <v>4</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>0.9</v>
@@ -3341,7 +3341,7 @@
         <v>4.2</v>
       </c>
       <c r="G33">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="H33">
         <v>0.65</v>
@@ -3400,7 +3400,7 @@
         <v>3.4</v>
       </c>
       <c r="G34">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="H34">
         <v>0.26</v>
@@ -3459,7 +3459,7 @@
         <v>5.25</v>
       </c>
       <c r="G35">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="H35">
         <v>0.8</v>
@@ -3518,7 +3518,7 @@
         <v>3.4</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H36">
         <v>0.14000000000000001</v>
@@ -3577,7 +3577,7 @@
         <v>6.4</v>
       </c>
       <c r="G37">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="H37">
         <v>0.9</v>
@@ -3636,7 +3636,7 @@
         <v>8</v>
       </c>
       <c r="G38">
-        <v>7.2</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="H38">
         <v>0.87</v>
@@ -3695,7 +3695,7 @@
         <v>6.5</v>
       </c>
       <c r="G39">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H39">
         <v>0.8</v>
@@ -3754,7 +3754,7 @@
         <v>7.3</v>
       </c>
       <c r="G40">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="H40">
         <v>0.52</v>
@@ -3813,7 +3813,7 @@
         <v>4.2</v>
       </c>
       <c r="G41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H41">
         <v>0.22</v>
@@ -3872,7 +3872,7 @@
         <v>5.75</v>
       </c>
       <c r="G42">
-        <v>7.25</v>
+        <v>8.25</v>
       </c>
       <c r="H42">
         <v>0.95</v>
@@ -3931,7 +3931,7 @@
         <v>2.4500000000000002</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43">
         <v>0.18</v>
@@ -3990,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="G44">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="H44">
         <v>0.71</v>
@@ -4049,7 +4049,7 @@
         <v>4.05</v>
       </c>
       <c r="G45">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="H45">
         <v>0.6</v>
@@ -4108,7 +4108,7 @@
         <v>10</v>
       </c>
       <c r="G46">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H46">
         <v>0.42</v>
@@ -4167,7 +4167,7 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="G47">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="H47">
         <v>0.24</v>
@@ -4226,7 +4226,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G48">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="H48">
         <v>1.1000000000000001</v>
@@ -4285,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>0.2</v>
@@ -4344,7 +4344,7 @@
         <v>7.6</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H50">
         <v>0.8</v>
@@ -4403,7 +4403,7 @@
         <v>2</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -4462,7 +4462,7 @@
         <v>7.15</v>
       </c>
       <c r="G52">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="H52">
         <v>0.51</v>
@@ -4521,7 +4521,7 @@
         <v>4.8</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H53">
         <v>0.2</v>
@@ -4580,7 +4580,7 @@
         <v>5</v>
       </c>
       <c r="G54">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H54">
         <v>0.75</v>
@@ -4639,7 +4639,7 @@
         <v>2.8</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H55">
         <v>0.14000000000000001</v>
@@ -4698,7 +4698,7 @@
         <v>8.9</v>
       </c>
       <c r="G56">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H56">
         <v>0.73</v>
@@ -4757,7 +4757,7 @@
         <v>5.8</v>
       </c>
       <c r="G57">
-        <v>4.9000000000000004</v>
+        <v>5.9</v>
       </c>
       <c r="H57">
         <v>0.83</v>
@@ -4816,7 +4816,7 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="G58">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="H58">
         <v>0.66</v>
@@ -4875,7 +4875,7 @@
         <v>9.1</v>
       </c>
       <c r="G59">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="H59">
         <v>0.79</v>
@@ -4934,7 +4934,7 @@
         <v>4</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60">
         <v>0.6</v>
@@ -4993,7 +4993,7 @@
         <v>2</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H61">
         <v>0.3</v>
@@ -5052,7 +5052,7 @@
         <v>5.5</v>
       </c>
       <c r="G62">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H62">
         <v>0.85</v>
@@ -5111,7 +5111,7 @@
         <v>2.15</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63">
         <v>0.16</v>
@@ -5170,7 +5170,7 @@
         <v>6.2</v>
       </c>
       <c r="G64">
-        <v>5.0999999999999996</v>
+        <v>6.1</v>
       </c>
       <c r="H64">
         <v>0.87</v>
@@ -5229,7 +5229,7 @@
         <v>3.8</v>
       </c>
       <c r="G65">
-        <v>3.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H65">
         <v>0.55000000000000004</v>

--- a/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
+++ b/ServeWay_Project/Assets/07.Data/FoodDataSet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jb944\Desktop\ServeWay\ServeWay_Project\Assets\07.Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5155F6B8-EC26-495E-9DE7-7C0333884EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3FC5A1E-25BE-42B6-8A25-08CE2946C3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
+    <workbookView xWindow="6870" yWindow="345" windowWidth="16125" windowHeight="14685" xr2:uid="{4D35103B-CB93-414B-994D-D848EB4BEE29}"/>
   </bookViews>
   <sheets>
     <sheet name="FoodDatas" sheetId="1" r:id="rId1"/>
@@ -784,21 +784,6 @@
     <t>_EffectPrefabPath</t>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/RiceBullet.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/BreadBullet.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Food1_Item.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/Item/Food1_Item.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>김치말이 국수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -961,13 +946,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/SoupBullet.prefab</t>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/SoupBullet.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7
 5</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1002,34 +980,6 @@
 4</t>
   </si>
   <si>
-    <t>Assets/05.Animations/EffectAnimation/FireEffect.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_f.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_c.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_p.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_sr.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Prefabs/TestPrefabs/CharacterBullet/MeatBullet_st.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/05.Animations/EffectAnimation/LaserEffect_2.prefab</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5
 5</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1053,6 +1003,47 @@
     <t>8
 6</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food1_Item</t>
+  </si>
+  <si>
+    <t>FireEffect</t>
+  </si>
+  <si>
+    <t>FireEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LaserEffect_2</t>
+  </si>
+  <si>
+    <t>LaserEffect_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet/SoupBullet</t>
+  </si>
+  <si>
+    <t>Bullet/RiceBullet</t>
+  </si>
+  <si>
+    <t>Bullet/BreadBullet</t>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_st</t>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_f</t>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_c</t>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_p</t>
+  </si>
+  <si>
+    <t>Bullet/MeatBullet_sr</t>
   </si>
 </sst>
 </file>
@@ -1483,13 +1474,13 @@
         <v>136</v>
       </c>
       <c r="Q1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="R1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
@@ -1527,19 +1518,19 @@
         <v>0.09</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="M2" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="N2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q2">
         <v>211</v>
@@ -1589,16 +1580,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N3" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="P3" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q3">
         <v>187</v>
@@ -1648,10 +1639,10 @@
         <v>2</v>
       </c>
       <c r="M4" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N4" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>30</v>
@@ -1707,10 +1698,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>32</v>
@@ -1766,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N6" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>33</v>
@@ -1789,7 +1780,7 @@
     </row>
     <row r="7" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1825,16 +1816,16 @@
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N7" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q7">
         <v>217</v>
@@ -1884,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N8" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>40</v>
@@ -1943,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N9" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>41</v>
@@ -2002,10 +1993,10 @@
         <v>1.5</v>
       </c>
       <c r="M10" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N10" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>42</v>
@@ -2025,7 +2016,7 @@
     </row>
     <row r="11" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -2061,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="M11" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N11" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="P11" t="s">
         <v>181</v>
@@ -2120,16 +2111,16 @@
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N12" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>43</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>219</v>
@@ -2176,13 +2167,13 @@
         <v>0.11</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="M13" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N13" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>44</v>
@@ -2202,7 +2193,7 @@
     </row>
     <row r="14" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B14">
         <v>12</v>
@@ -2238,16 +2229,16 @@
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N14" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q14">
         <v>252</v>
@@ -2297,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>51</v>
@@ -2356,10 +2347,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>52</v>
@@ -2412,13 +2403,13 @@
         <v>0.06</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="M17" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N17" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>53</v>
@@ -2474,16 +2465,16 @@
         <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N18" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="P18" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q18">
         <v>171</v>
@@ -2533,10 +2524,10 @@
         <v>0.9</v>
       </c>
       <c r="M19" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N19" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>55</v>
@@ -2592,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N20" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>61</v>
@@ -2651,10 +2642,10 @@
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>62</v>
@@ -2707,13 +2698,13 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N22" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>63</v>
@@ -2733,7 +2724,7 @@
     </row>
     <row r="23" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B23">
         <v>21</v>
@@ -2769,13 +2760,13 @@
         <v>1.3</v>
       </c>
       <c r="M23" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N23" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="P23" t="s">
         <v>181</v>
@@ -2828,10 +2819,10 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="M24" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N24" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>134</v>
@@ -2851,7 +2842,7 @@
     </row>
     <row r="25" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B25">
         <v>23</v>
@@ -2887,13 +2878,13 @@
         <v>1.9</v>
       </c>
       <c r="M25" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N25" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P25" t="s">
         <v>181</v>
@@ -2910,7 +2901,7 @@
     </row>
     <row r="26" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B26">
         <v>24</v>
@@ -2946,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N26" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="P26" t="s">
         <v>181</v>
@@ -3005,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N27" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>70</v>
@@ -3064,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N28" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>71</v>
@@ -3120,13 +3111,13 @@
         <v>0.03</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="M29" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N29" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>72</v>
@@ -3182,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N30" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>73</v>
       </c>
       <c r="P30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q30">
         <v>241</v>
@@ -3241,10 +3232,10 @@
         <v>2.1</v>
       </c>
       <c r="M31" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N31" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>74</v>
@@ -3264,7 +3255,7 @@
     </row>
     <row r="32" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B32">
         <v>30</v>
@@ -3297,19 +3288,19 @@
         <v>0.1</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N32" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="P32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q32">
         <v>249</v>
@@ -3359,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N33" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>81</v>
@@ -3418,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>82</v>
@@ -3474,13 +3465,13 @@
         <v>0.03</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>83</v>
@@ -3536,16 +3527,16 @@
         <v>0</v>
       </c>
       <c r="M36" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N36" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>84</v>
       </c>
       <c r="P36" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q36">
         <v>227</v>
@@ -3595,10 +3586,10 @@
         <v>1.7</v>
       </c>
       <c r="M37" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N37" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>85</v>
@@ -3618,7 +3609,7 @@
     </row>
     <row r="38" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B38">
         <v>36</v>
@@ -3654,13 +3645,13 @@
         <v>2.1</v>
       </c>
       <c r="M38" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N38" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="P38" t="s">
         <v>181</v>
@@ -3677,7 +3668,7 @@
     </row>
     <row r="39" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B39">
         <v>37</v>
@@ -3710,16 +3701,16 @@
         <v>0.05</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N39" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P39" t="s">
         <v>181</v>
@@ -3748,7 +3739,7 @@
         <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F40">
         <v>7.3</v>
@@ -3772,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N40" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>92</v>
@@ -3831,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N41" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>93</v>
@@ -3887,13 +3878,13 @@
         <v>0.05</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="M42" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N42" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>94</v>
@@ -3949,16 +3940,16 @@
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N43" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>95</v>
       </c>
       <c r="P43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q43">
         <v>172</v>
@@ -4008,10 +3999,10 @@
         <v>2</v>
       </c>
       <c r="M44" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N44" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>96</v>
@@ -4031,7 +4022,7 @@
     </row>
     <row r="45" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B45">
         <v>43</v>
@@ -4067,13 +4058,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N45" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="P45" t="s">
         <v>181</v>
@@ -4126,10 +4117,10 @@
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N46" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>133</v>
@@ -4185,10 +4176,10 @@
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N47" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>102</v>
@@ -4241,13 +4232,13 @@
         <v>0.08</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="M48" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N48" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>103</v>
@@ -4303,16 +4294,16 @@
         <v>0</v>
       </c>
       <c r="M49" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N49" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>104</v>
       </c>
       <c r="P49" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q49">
         <v>185</v>
@@ -4326,7 +4317,7 @@
     </row>
     <row r="50" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B50">
         <v>48</v>
@@ -4362,13 +4353,13 @@
         <v>2</v>
       </c>
       <c r="M50" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N50" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P50" t="s">
         <v>181</v>
@@ -4385,7 +4376,7 @@
     </row>
     <row r="51" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B51">
         <v>49</v>
@@ -4418,16 +4409,16 @@
         <v>0.1</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="M51" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N51" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P51" t="s">
         <v>181</v>
@@ -4480,10 +4471,10 @@
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N52" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O52" s="1" t="s">
         <v>113</v>
@@ -4539,10 +4530,10 @@
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N53" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>114</v>
@@ -4595,13 +4586,13 @@
         <v>0.03</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="M54" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N54" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O54" s="1" t="s">
         <v>115</v>
@@ -4657,16 +4648,16 @@
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N55" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O55" s="1" t="s">
         <v>116</v>
       </c>
       <c r="P55" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="Q55">
         <v>233</v>
@@ -4716,10 +4707,10 @@
         <v>2.5</v>
       </c>
       <c r="M56" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N56" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>117</v>
@@ -4775,10 +4766,10 @@
         <v>1.4</v>
       </c>
       <c r="M57" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N57" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>118</v>
@@ -4834,10 +4825,10 @@
         <v>0</v>
       </c>
       <c r="M58" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N58" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>119</v>
@@ -4857,7 +4848,7 @@
     </row>
     <row r="59" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B59">
         <v>57</v>
@@ -4893,13 +4884,13 @@
         <v>2.5</v>
       </c>
       <c r="M59" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N59" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="P59" t="s">
         <v>181</v>
@@ -4952,10 +4943,10 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N60" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>127</v>
@@ -5011,10 +5002,10 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N61" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>128</v>
@@ -5067,13 +5058,13 @@
         <v>0.03</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="M62" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N62" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>129</v>
@@ -5129,16 +5120,16 @@
         <v>0</v>
       </c>
       <c r="M63" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N63" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>130</v>
       </c>
       <c r="P63" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="Q63">
         <v>182</v>
@@ -5188,10 +5179,10 @@
         <v>1.6</v>
       </c>
       <c r="M64" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N64" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>131</v>
@@ -5247,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
       <c r="N65" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>132</v>
